--- a/output/roomself_excel/9846.xlsx
+++ b/output/roomself_excel/9846.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,20 +466,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>108265</v>
+        <v>73974</v>
       </c>
       <c r="D2" t="n">
-        <v>2648</v>
+        <v>2296</v>
       </c>
       <c r="E2" t="n">
-        <v>398</v>
+        <v>235</v>
       </c>
       <c r="F2" t="n">
-        <v>313</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3">
@@ -492,16 +492,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>232380</v>
+        <v>158406</v>
       </c>
       <c r="D3" t="n">
-        <v>5156</v>
+        <v>3212</v>
       </c>
       <c r="E3" t="n">
-        <v>584</v>
+        <v>349</v>
       </c>
       <c r="F3" t="n">
-        <v>121</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4">
@@ -510,20 +510,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>30310</v>
+        <v>108265</v>
       </c>
       <c r="D4" t="n">
-        <v>1584</v>
+        <v>2648</v>
       </c>
       <c r="E4" t="n">
-        <v>274</v>
+        <v>398</v>
       </c>
       <c r="F4" t="n">
-        <v>158</v>
+        <v>313</v>
       </c>
     </row>
     <row r="5">
@@ -532,20 +532,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>73962</v>
+        <v>95347</v>
       </c>
       <c r="D5" t="n">
-        <v>2456</v>
+        <v>2512</v>
       </c>
       <c r="E5" t="n">
-        <v>254</v>
+        <v>74</v>
       </c>
       <c r="F5" t="n">
-        <v>100</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6">
@@ -554,20 +554,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>95347</v>
+        <v>30310</v>
       </c>
       <c r="D6" t="n">
-        <v>2512</v>
+        <v>1584</v>
       </c>
       <c r="E6" t="n">
-        <v>74</v>
+        <v>195</v>
       </c>
       <c r="F6" t="n">
-        <v>19</v>
+        <v>158</v>
       </c>
     </row>
     <row r="7">
@@ -576,14 +576,14 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>7810</v>
+        <v>73962</v>
       </c>
       <c r="D7" t="n">
-        <v>724</v>
+        <v>2456</v>
       </c>
       <c r="E7" t="n">
         <v>110</v>
@@ -602,15 +602,37 @@
         </is>
       </c>
       <c r="C8" t="n">
+        <v>7810</v>
+      </c>
+      <c r="D8" t="n">
+        <v>724</v>
+      </c>
+      <c r="E8" t="n">
+        <v>110</v>
+      </c>
+      <c r="F8" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
         <v>4416</v>
       </c>
-      <c r="D8" t="n">
+      <c r="D9" t="n">
         <v>568</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E9" t="n">
         <v>96</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F9" t="n">
         <v>18</v>
       </c>
     </row>

--- a/output/roomself_excel/9846.xlsx
+++ b/output/roomself_excel/9846.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:M9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,47 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallLength</t>
+          <t>WallDir_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallWidth</t>
+          <t>ExtWallLength_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_2</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_3</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_3</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_3</t>
         </is>
       </c>
     </row>
@@ -475,12 +510,23 @@
       <c r="D2" t="n">
         <v>2296</v>
       </c>
-      <c r="E2" t="n">
-        <v>235</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F2" t="n">
-        <v>42</v>
-      </c>
+        <v>204</v>
+      </c>
+      <c r="G2" t="n">
+        <v>31</v>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -497,12 +543,31 @@
       <c r="D3" t="n">
         <v>3212</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
         <v>349</v>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>23</v>
       </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>426</v>
+      </c>
+      <c r="J3" t="n">
+        <v>29</v>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -519,12 +584,31 @@
       <c r="D4" t="n">
         <v>2648</v>
       </c>
-      <c r="E4" t="n">
-        <v>398</v>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F4" t="n">
-        <v>313</v>
-      </c>
+        <v>295</v>
+      </c>
+      <c r="G4" t="n">
+        <v>31</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>367</v>
+      </c>
+      <c r="J4" t="n">
+        <v>18</v>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -541,11 +625,38 @@
       <c r="D5" t="n">
         <v>2512</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>257</v>
+      </c>
+      <c r="G5" t="n">
+        <v>29</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
         <v>74</v>
       </c>
-      <c r="F5" t="n">
+      <c r="J5" t="n">
         <v>19</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>371</v>
+      </c>
+      <c r="M5" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="6">
@@ -563,12 +674,31 @@
       <c r="D6" t="n">
         <v>1584</v>
       </c>
-      <c r="E6" t="n">
-        <v>195</v>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F6" t="n">
-        <v>158</v>
-      </c>
+        <v>177</v>
+      </c>
+      <c r="G6" t="n">
+        <v>18</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>140</v>
+      </c>
+      <c r="J6" t="n">
+        <v>18</v>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -585,12 +715,23 @@
       <c r="D7" t="n">
         <v>2456</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
         <v>110</v>
       </c>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
         <v>18</v>
       </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -607,12 +748,23 @@
       <c r="D8" t="n">
         <v>724</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
         <v>110</v>
       </c>
-      <c r="F8" t="n">
+      <c r="G8" t="n">
         <v>18</v>
       </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -629,12 +781,23 @@
       <c r="D9" t="n">
         <v>568</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
         <v>96</v>
       </c>
-      <c r="F9" t="n">
+      <c r="G9" t="n">
         <v>18</v>
       </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
